--- a/artfynd/A 61675-2023 artfynd.xlsx
+++ b/artfynd/A 61675-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130660533</v>
       </c>
       <c r="B2" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61675-2023 artfynd.xlsx
+++ b/artfynd/A 61675-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130660533</v>
       </c>
       <c r="B2" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61675-2023 artfynd.xlsx
+++ b/artfynd/A 61675-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130660533</v>
       </c>
       <c r="B2" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61675-2023 artfynd.xlsx
+++ b/artfynd/A 61675-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130660533</v>
       </c>
       <c r="B2" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61675-2023 artfynd.xlsx
+++ b/artfynd/A 61675-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130660533</v>
+        <v>130660504</v>
       </c>
       <c r="B2" t="n">
-        <v>57881</v>
+        <v>77726</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,26 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1342</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>373504</v>
+        <v>373525</v>
       </c>
       <c r="R2" t="n">
-        <v>6314098</v>
+        <v>6314104</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,11 +757,6 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ropande</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -765,6 +765,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -774,10 +789,1059 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
+          <t>Alice Hennig, Elsa Fogelström</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>130660517</v>
+      </c>
+      <c r="B3" t="n">
+        <v>97811</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2604</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Trädporella</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Porella platyphylla</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Pfeiff.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bästhult, Hl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>373526</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6314161</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hylte</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Drängsered</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Alice Hennig</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Alice Hennig, Elsa Fogelström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130660502</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97785</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2606</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Klippfrullania</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Frullania tamarisci</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bästhult, Hl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>373522</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6314087</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hylte</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Drängsered</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Alice Hennig</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Alice Hennig, Elsa Fogelström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130660507</v>
+      </c>
+      <c r="B5" t="n">
+        <v>96437</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bästhult, Hl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>373522</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6314109</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hylte</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Drängsered</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Alice Hennig</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Alice Hennig, Elsa Fogelström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130660512</v>
+      </c>
+      <c r="B6" t="n">
+        <v>96426</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bästhult, Hl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>373528</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6314141</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hylte</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Drängsered</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Alice Hennig</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Alice Hennig, Elsa Fogelström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130660506</v>
+      </c>
+      <c r="B7" t="n">
+        <v>96231</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bästhult, Hl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>373514</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6314106</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hylte</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Drängsered</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Alice Hennig</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Alice Hennig, Elsa Fogelström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130660533</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bästhult, Hl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>373504</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6314098</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hylte</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Drängsered</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ropande</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Alice Hennig</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Alice Hennig</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130660503</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bästhult, Hl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>373511</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6314101</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hylte</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Drängsered</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Alice Hennig</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Alice Hennig, Elsa Fogelström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130660509</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bästhult, Hl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>373524</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6314123</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hylte</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Drängsered</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Alice Hennig</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Alice Hennig, Elsa Fogelström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130660515</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bästhult, Hl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>373525</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6314164</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hylte</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Drängsered</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Alice Hennig</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Alice Hennig, Elsa Fogelström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61675-2023 artfynd.xlsx
+++ b/artfynd/A 61675-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130660504</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,6 +919,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130660517</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1025,6 +1040,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130660502</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1146,6 +1166,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130660507</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1267,6 +1292,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130660512</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1388,6 +1418,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130660506</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1494,6 +1529,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130660533</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1615,6 +1655,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130660503</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1721,6 +1766,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130660509</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1842,8 +1892,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130660515</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>